--- a/target/test-classes/testdata/SignInData.xlsx
+++ b/target/test-classes/testdata/SignInData.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Local\DXC\iot-fe-automation\src\test\resources\testdata\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\maria\Downloads\QA_Automation\s2-selenium\src\test\resources\testdata\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{10B19F07-D767-4660-A92F-0B9AE64AA9CC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{808FB7BB-8430-417C-874C-54EBD606B1D7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="12710" yWindow="0" windowWidth="12980" windowHeight="13770" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="22695" windowHeight="14476" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="signin" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="54" uniqueCount="25">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="27" uniqueCount="25">
   <si>
     <t>testCaseId</t>
   </si>
@@ -94,7 +94,7 @@
     <t>valid@test.com</t>
   </si>
   <si>
-    <t>Pass@123</t>
+    <t>Pass123#</t>
   </si>
 </sst>
 </file>
@@ -497,7 +497,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:F5"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="13" customWidth="1"/>
     <col min="2" max="2" width="21" customWidth="1"/>
@@ -507,7 +507,7 @@
     <col min="6" max="6" width="24" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -527,7 +527,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A2" s="2" t="s">
         <v>6</v>
       </c>
@@ -545,7 +545,7 @@
       </c>
       <c r="F2" s="2"/>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A3" s="3" t="s">
         <v>9</v>
       </c>
@@ -565,7 +565,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A4" s="2" t="s">
         <v>14</v>
       </c>
@@ -581,7 +581,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A5" s="3" t="s">
         <v>18</v>
       </c>
@@ -603,7 +603,7 @@
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="D2" r:id="rId1" xr:uid="{3CDB61D4-EA7C-4BA5-BE58-F8F5605B15C4}"/>
+    <hyperlink ref="D2" r:id="rId1" display="Pass@123" xr:uid="{3CDB61D4-EA7C-4BA5-BE58-F8F5605B15C4}"/>
     <hyperlink ref="C2" r:id="rId2" xr:uid="{2886B8FC-4413-42DB-B3E4-E55F368CEDD4}"/>
     <hyperlink ref="C3" r:id="rId3" xr:uid="{08D1A5F6-365B-4D82-9238-7207719CC13E}"/>
     <hyperlink ref="C5" r:id="rId4" xr:uid="{27226942-BA7F-4A73-9C28-F8DD44791D1D}"/>
